--- a/resultados/siqueiracampos/inventario_externos.xlsx
+++ b/resultados/siqueiracampos/inventario_externos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/resultados/siqueiracampos/inventario_externos.xlsx
+++ b/resultados/siqueiracampos/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7802,6 +7802,286 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://pt.wikipedia.org/wiki/S%C3%A3o_Jos%C3%A9</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>pt.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>São José Operário</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2253/missa-do-trabalhador-de-2021/</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>5</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:36:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://pt.wikipedia.org/wiki/Trabalhadores</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>pt.wikipedia.org</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>trabalhadores</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2253/missa-do-trabalhador-de-2021/</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>5</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:36:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://bit.ly/2NLeh6M</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Inscreva-se PSS 04/2021</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/409/inscricoes-abertas-pss-042021/</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>5</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:36:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://www.npdiario.com.br/cidades/equipe-de-truco-de-siqueira-campos-compete-em-campeonato/</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>www.npdiario.com.br</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>(npdiario.com.br)</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2488/equipe-de-truco-de-siqueira-campos-conquista-vitorias/</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>5</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:50:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://www.saude.pr.gov.br/Noticia/Risco-de-obito-por-Covid-19-e-22-vezes-menor-entre-vacinados-com-dose-de-reforco-aponta</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>www.saude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Secretaria da Saúde (saude.pr.gov.br)</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2454/risco-de-obito-por-covid-19-e-quase-9-vezes-menor-entre-pessoas-com-esquema-vacinal-completo-aponta-estudo/</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>5</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:55:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3c6F5aS</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Agendar vacinação</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/408/cronograma-de-vacinacao-4-semana-de-marco/</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>5</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:58:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://abre.ai/agendar-vacinasiq?fbclid=IwAR3GpcAn_0_KR260SwgNCDHBzTuRfMqOoZDVGbChqViLYRY5tVmTyenwtdI</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>abre.ai</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>https://abre.ai/agendar-vacinasiq</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2264/cronograma-da-vacina/</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>5</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:58:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://abre.ai/local-triagem-covid</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>abre.ai</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Novo Local Triagem Covid-19</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2263/novo-local-centro-de-triagem/</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>5</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:58:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/siqueiracampos/inventario_externos.xlsx
+++ b/resultados/siqueiracampos/inventario_externos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8082,6 +8082,286 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://bityli.com/RLS3V</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>bityli.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DOCUMENTO SOLICITAÇÃO DE RECURSO</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2381/pss-saude-classificacao-preliminar-divulgada/</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>6</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-08-11 18:54:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3B3VSoP?fbclid=IwAR3sIuyuCeNoxoxZdPExIwhY2xD19dist-P4JZSep7TKl-KW7q0b8oT7DpM</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3B3VSoP</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2370/pss-saude-novo-cronograma/</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>6</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-08-11 18:57:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://api.whatsapp.com/send?phone=554335711183&amp;text=Ol%C3%A1%2C%20eu%20estou%20na%20fase%20vigente%20da%20vacina%C3%A7%C3%A3o%20e%20gostaria%20de%20agendar.</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>api.whatsapp.com</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI PARA AGENDAR SUA VACINA</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2311/chegou-sua-vez-de-vacinar/</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>6</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-08-11 19:07:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSccTtzjBLQXNf8rIESsa_lntdx3oDtso0bfhVTSnH2s7zHxWg/viewform</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CADASTRO FILA DA VACINA</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2311/chegou-sua-vez-de-vacinar/</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>6</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-08-11 19:07:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3B3VSoP</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3B3VSoP</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2356/inscricoes-abertas-para-pss-da-saude/</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>7</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-08-11 20:52:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>http://abre.ai/educapss</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>abre.ai</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>http://abre.ai/educapss</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/428/inscricoes-abertas-para-o-pss-educacao/</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>4</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:30:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://cutt.ly/QlO06iU?fbclid=IwAR2ZQo9LJ3PwsO4ud7jtRwm_uNFB5weII63fIyeR9Dpj1zW6hY8igWhhVkE</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>cutt.ly</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://cutt.ly/QlO06iU</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/418/inscricoes-abertas-pss-03-2021-obras/</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>4</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:30:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3q1bKSS?fbclid=IwAR0y6ru5qReO_L4XMRnyfwKO34J7_1uVYEZ6FDY61ncabn59bBTqNuLjhKU</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>bit.ly</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3q1bKSS</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/420/edital-pss-032021/</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>4</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:30:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
